--- a/templates/05_nominatif.xlsx
+++ b/templates/05_nominatif.xlsx
@@ -2454,19 +2454,25 @@
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="4" t="s">
-        <v>132</v>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group Head Operasional SDM</t>
+        </is>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="4" t="s">
-        <v>133</v>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department Head Kompensasi dan Benefit</t>
+        </is>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
-      <c r="N42" s="4" t="s">
-        <v>134</v>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staf Kompensasi dan Benefit</t>
+        </is>
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
@@ -2580,19 +2586,25 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="4" t="s">
-        <v>135</v>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yogi Permana</t>
+        </is>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="4" t="s">
-        <v>136</v>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rini Kartika Sari</t>
+        </is>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
-      <c r="N48" s="4" t="s">
-        <v>137</v>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shafira Adi Rabiah Al Adawiyah</t>
+        </is>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
